--- a/apps/account-lookup/アカウント名簿テンプレート.xlsx
+++ b/apps/account-lookup/アカウント名簿テンプレート.xlsx
@@ -17,13 +17,22 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C8531B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -35,12 +44,17 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCEEE3"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -79,21 +93,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -470,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -482,623 +500,642 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="70" customWidth="1" min="11" max="11"/>
+    <col width="76" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>まなびポケット学校コード（全員共通）</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>◀ まなびポケット学校コードは「全員共通」です。すぐ下のセル（A2）に1つだけ入力してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>manabi-1234</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
           <t>年</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>組</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>番</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>氏名（漢字）</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>氏名（ひらがな）</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Googleアカウント</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Googleパスワード</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>端末番号</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>端末暗証番号</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>◀ この行が見出しです（消さないでください）。「氏名（ひらがな）」で検索します。記入例の3行は上書きまたは削除して使ってください。端末暗証番号などの先頭の 0 は、この列が『文字列』設定なのでそのまま保てます。</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
+    <row r="4">
+      <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>山田 太郎</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>やまだ たろう</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>taro.yamada@example-jhs.ed.jp</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Yamada-1234</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>T-001</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>0042</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
+    <row r="5">
+      <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>佐藤 花子</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>さとう はなこ</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>hanako.sato@example-jhs.ed.jp</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Sato-5678</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>T-002</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>0157</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
+    <row r="6">
+      <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C6" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>鈴木 一郎</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>すずき いちろう</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>ichiro.suzuki@example-jhs.ed.jp</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>Suzuki-9012</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>T-115</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>0830</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr"/>
-      <c r="B5" s="6" t="inlineStr"/>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr"/>
-      <c r="B6" s="6" t="inlineStr"/>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
-    </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr"/>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="8" t="inlineStr"/>
+      <c r="A7" s="8" t="inlineStr"/>
+      <c r="B7" s="8" t="inlineStr"/>
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr"/>
+      <c r="E7" s="9" t="inlineStr"/>
+      <c r="F7" s="10" t="inlineStr"/>
+      <c r="G7" s="10" t="inlineStr"/>
+      <c r="H7" s="10" t="inlineStr"/>
+      <c r="I7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr"/>
-      <c r="B8" s="6" t="inlineStr"/>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr"/>
-      <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="8" t="inlineStr"/>
+      <c r="A8" s="8" t="inlineStr"/>
+      <c r="B8" s="8" t="inlineStr"/>
+      <c r="C8" s="8" t="inlineStr"/>
+      <c r="D8" s="9" t="inlineStr"/>
+      <c r="E8" s="9" t="inlineStr"/>
+      <c r="F8" s="10" t="inlineStr"/>
+      <c r="G8" s="10" t="inlineStr"/>
+      <c r="H8" s="10" t="inlineStr"/>
+      <c r="I8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr"/>
-      <c r="B9" s="6" t="inlineStr"/>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="8" t="inlineStr"/>
+      <c r="A9" s="8" t="inlineStr"/>
+      <c r="B9" s="8" t="inlineStr"/>
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="9" t="inlineStr"/>
+      <c r="E9" s="9" t="inlineStr"/>
+      <c r="F9" s="10" t="inlineStr"/>
+      <c r="G9" s="10" t="inlineStr"/>
+      <c r="H9" s="10" t="inlineStr"/>
+      <c r="I9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr"/>
-      <c r="B10" s="6" t="inlineStr"/>
-      <c r="C10" s="6" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr"/>
-      <c r="I10" s="8" t="inlineStr"/>
+      <c r="A10" s="8" t="inlineStr"/>
+      <c r="B10" s="8" t="inlineStr"/>
+      <c r="C10" s="8" t="inlineStr"/>
+      <c r="D10" s="9" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr"/>
+      <c r="F10" s="10" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr"/>
+      <c r="H10" s="10" t="inlineStr"/>
+      <c r="I10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr"/>
-      <c r="B11" s="6" t="inlineStr"/>
-      <c r="C11" s="6" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="8" t="inlineStr"/>
-      <c r="H11" s="8" t="inlineStr"/>
-      <c r="I11" s="8" t="inlineStr"/>
+      <c r="A11" s="8" t="inlineStr"/>
+      <c r="B11" s="8" t="inlineStr"/>
+      <c r="C11" s="8" t="inlineStr"/>
+      <c r="D11" s="9" t="inlineStr"/>
+      <c r="E11" s="9" t="inlineStr"/>
+      <c r="F11" s="10" t="inlineStr"/>
+      <c r="G11" s="10" t="inlineStr"/>
+      <c r="H11" s="10" t="inlineStr"/>
+      <c r="I11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr"/>
-      <c r="B12" s="6" t="inlineStr"/>
-      <c r="C12" s="6" t="inlineStr"/>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="8" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="8" t="inlineStr"/>
+      <c r="A12" s="8" t="inlineStr"/>
+      <c r="B12" s="8" t="inlineStr"/>
+      <c r="C12" s="8" t="inlineStr"/>
+      <c r="D12" s="9" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="10" t="inlineStr"/>
+      <c r="G12" s="10" t="inlineStr"/>
+      <c r="H12" s="10" t="inlineStr"/>
+      <c r="I12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr"/>
-      <c r="B13" s="6" t="inlineStr"/>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
-      <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="8" t="inlineStr"/>
-      <c r="I13" s="8" t="inlineStr"/>
+      <c r="A13" s="8" t="inlineStr"/>
+      <c r="B13" s="8" t="inlineStr"/>
+      <c r="C13" s="8" t="inlineStr"/>
+      <c r="D13" s="9" t="inlineStr"/>
+      <c r="E13" s="9" t="inlineStr"/>
+      <c r="F13" s="10" t="inlineStr"/>
+      <c r="G13" s="10" t="inlineStr"/>
+      <c r="H13" s="10" t="inlineStr"/>
+      <c r="I13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr"/>
-      <c r="B14" s="6" t="inlineStr"/>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="7" t="inlineStr"/>
-      <c r="E14" s="7" t="inlineStr"/>
-      <c r="F14" s="8" t="inlineStr"/>
-      <c r="G14" s="8" t="inlineStr"/>
-      <c r="H14" s="8" t="inlineStr"/>
-      <c r="I14" s="8" t="inlineStr"/>
+      <c r="A14" s="8" t="inlineStr"/>
+      <c r="B14" s="8" t="inlineStr"/>
+      <c r="C14" s="8" t="inlineStr"/>
+      <c r="D14" s="9" t="inlineStr"/>
+      <c r="E14" s="9" t="inlineStr"/>
+      <c r="F14" s="10" t="inlineStr"/>
+      <c r="G14" s="10" t="inlineStr"/>
+      <c r="H14" s="10" t="inlineStr"/>
+      <c r="I14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr"/>
-      <c r="B15" s="6" t="inlineStr"/>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="7" t="inlineStr"/>
-      <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr"/>
-      <c r="G15" s="8" t="inlineStr"/>
-      <c r="H15" s="8" t="inlineStr"/>
-      <c r="I15" s="8" t="inlineStr"/>
+      <c r="A15" s="8" t="inlineStr"/>
+      <c r="B15" s="8" t="inlineStr"/>
+      <c r="C15" s="8" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr"/>
-      <c r="B16" s="6" t="inlineStr"/>
-      <c r="C16" s="6" t="inlineStr"/>
-      <c r="D16" s="7" t="inlineStr"/>
-      <c r="E16" s="7" t="inlineStr"/>
-      <c r="F16" s="8" t="inlineStr"/>
-      <c r="G16" s="8" t="inlineStr"/>
-      <c r="H16" s="8" t="inlineStr"/>
-      <c r="I16" s="8" t="inlineStr"/>
+      <c r="A16" s="8" t="inlineStr"/>
+      <c r="B16" s="8" t="inlineStr"/>
+      <c r="C16" s="8" t="inlineStr"/>
+      <c r="D16" s="9" t="inlineStr"/>
+      <c r="E16" s="9" t="inlineStr"/>
+      <c r="F16" s="10" t="inlineStr"/>
+      <c r="G16" s="10" t="inlineStr"/>
+      <c r="H16" s="10" t="inlineStr"/>
+      <c r="I16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr"/>
-      <c r="B17" s="6" t="inlineStr"/>
-      <c r="C17" s="6" t="inlineStr"/>
-      <c r="D17" s="7" t="inlineStr"/>
-      <c r="E17" s="7" t="inlineStr"/>
-      <c r="F17" s="8" t="inlineStr"/>
-      <c r="G17" s="8" t="inlineStr"/>
-      <c r="H17" s="8" t="inlineStr"/>
-      <c r="I17" s="8" t="inlineStr"/>
+      <c r="A17" s="8" t="inlineStr"/>
+      <c r="B17" s="8" t="inlineStr"/>
+      <c r="C17" s="8" t="inlineStr"/>
+      <c r="D17" s="9" t="inlineStr"/>
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="10" t="inlineStr"/>
+      <c r="G17" s="10" t="inlineStr"/>
+      <c r="H17" s="10" t="inlineStr"/>
+      <c r="I17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr"/>
-      <c r="B18" s="6" t="inlineStr"/>
-      <c r="C18" s="6" t="inlineStr"/>
-      <c r="D18" s="7" t="inlineStr"/>
-      <c r="E18" s="7" t="inlineStr"/>
-      <c r="F18" s="8" t="inlineStr"/>
-      <c r="G18" s="8" t="inlineStr"/>
-      <c r="H18" s="8" t="inlineStr"/>
-      <c r="I18" s="8" t="inlineStr"/>
+      <c r="A18" s="8" t="inlineStr"/>
+      <c r="B18" s="8" t="inlineStr"/>
+      <c r="C18" s="8" t="inlineStr"/>
+      <c r="D18" s="9" t="inlineStr"/>
+      <c r="E18" s="9" t="inlineStr"/>
+      <c r="F18" s="10" t="inlineStr"/>
+      <c r="G18" s="10" t="inlineStr"/>
+      <c r="H18" s="10" t="inlineStr"/>
+      <c r="I18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr"/>
-      <c r="B19" s="6" t="inlineStr"/>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr"/>
-      <c r="E19" s="7" t="inlineStr"/>
-      <c r="F19" s="8" t="inlineStr"/>
-      <c r="G19" s="8" t="inlineStr"/>
-      <c r="H19" s="8" t="inlineStr"/>
-      <c r="I19" s="8" t="inlineStr"/>
+      <c r="A19" s="8" t="inlineStr"/>
+      <c r="B19" s="8" t="inlineStr"/>
+      <c r="C19" s="8" t="inlineStr"/>
+      <c r="D19" s="9" t="inlineStr"/>
+      <c r="E19" s="9" t="inlineStr"/>
+      <c r="F19" s="10" t="inlineStr"/>
+      <c r="G19" s="10" t="inlineStr"/>
+      <c r="H19" s="10" t="inlineStr"/>
+      <c r="I19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr"/>
-      <c r="B20" s="6" t="inlineStr"/>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="7" t="inlineStr"/>
-      <c r="E20" s="7" t="inlineStr"/>
-      <c r="F20" s="8" t="inlineStr"/>
-      <c r="G20" s="8" t="inlineStr"/>
-      <c r="H20" s="8" t="inlineStr"/>
-      <c r="I20" s="8" t="inlineStr"/>
+      <c r="A20" s="8" t="inlineStr"/>
+      <c r="B20" s="8" t="inlineStr"/>
+      <c r="C20" s="8" t="inlineStr"/>
+      <c r="D20" s="9" t="inlineStr"/>
+      <c r="E20" s="9" t="inlineStr"/>
+      <c r="F20" s="10" t="inlineStr"/>
+      <c r="G20" s="10" t="inlineStr"/>
+      <c r="H20" s="10" t="inlineStr"/>
+      <c r="I20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr"/>
-      <c r="B21" s="6" t="inlineStr"/>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="7" t="inlineStr"/>
-      <c r="E21" s="7" t="inlineStr"/>
-      <c r="F21" s="8" t="inlineStr"/>
-      <c r="G21" s="8" t="inlineStr"/>
-      <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="8" t="inlineStr"/>
+      <c r="A21" s="8" t="inlineStr"/>
+      <c r="B21" s="8" t="inlineStr"/>
+      <c r="C21" s="8" t="inlineStr"/>
+      <c r="D21" s="9" t="inlineStr"/>
+      <c r="E21" s="9" t="inlineStr"/>
+      <c r="F21" s="10" t="inlineStr"/>
+      <c r="G21" s="10" t="inlineStr"/>
+      <c r="H21" s="10" t="inlineStr"/>
+      <c r="I21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr"/>
-      <c r="B22" s="6" t="inlineStr"/>
-      <c r="C22" s="6" t="inlineStr"/>
-      <c r="D22" s="7" t="inlineStr"/>
-      <c r="E22" s="7" t="inlineStr"/>
-      <c r="F22" s="8" t="inlineStr"/>
-      <c r="G22" s="8" t="inlineStr"/>
-      <c r="H22" s="8" t="inlineStr"/>
-      <c r="I22" s="8" t="inlineStr"/>
+      <c r="A22" s="8" t="inlineStr"/>
+      <c r="B22" s="8" t="inlineStr"/>
+      <c r="C22" s="8" t="inlineStr"/>
+      <c r="D22" s="9" t="inlineStr"/>
+      <c r="E22" s="9" t="inlineStr"/>
+      <c r="F22" s="10" t="inlineStr"/>
+      <c r="G22" s="10" t="inlineStr"/>
+      <c r="H22" s="10" t="inlineStr"/>
+      <c r="I22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr"/>
-      <c r="B23" s="6" t="inlineStr"/>
-      <c r="C23" s="6" t="inlineStr"/>
-      <c r="D23" s="7" t="inlineStr"/>
-      <c r="E23" s="7" t="inlineStr"/>
-      <c r="F23" s="8" t="inlineStr"/>
-      <c r="G23" s="8" t="inlineStr"/>
-      <c r="H23" s="8" t="inlineStr"/>
-      <c r="I23" s="8" t="inlineStr"/>
+      <c r="A23" s="8" t="inlineStr"/>
+      <c r="B23" s="8" t="inlineStr"/>
+      <c r="C23" s="8" t="inlineStr"/>
+      <c r="D23" s="9" t="inlineStr"/>
+      <c r="E23" s="9" t="inlineStr"/>
+      <c r="F23" s="10" t="inlineStr"/>
+      <c r="G23" s="10" t="inlineStr"/>
+      <c r="H23" s="10" t="inlineStr"/>
+      <c r="I23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr"/>
-      <c r="B24" s="6" t="inlineStr"/>
-      <c r="C24" s="6" t="inlineStr"/>
-      <c r="D24" s="7" t="inlineStr"/>
-      <c r="E24" s="7" t="inlineStr"/>
-      <c r="F24" s="8" t="inlineStr"/>
-      <c r="G24" s="8" t="inlineStr"/>
-      <c r="H24" s="8" t="inlineStr"/>
-      <c r="I24" s="8" t="inlineStr"/>
+      <c r="A24" s="8" t="inlineStr"/>
+      <c r="B24" s="8" t="inlineStr"/>
+      <c r="C24" s="8" t="inlineStr"/>
+      <c r="D24" s="9" t="inlineStr"/>
+      <c r="E24" s="9" t="inlineStr"/>
+      <c r="F24" s="10" t="inlineStr"/>
+      <c r="G24" s="10" t="inlineStr"/>
+      <c r="H24" s="10" t="inlineStr"/>
+      <c r="I24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr"/>
-      <c r="B25" s="6" t="inlineStr"/>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="7" t="inlineStr"/>
-      <c r="E25" s="7" t="inlineStr"/>
-      <c r="F25" s="8" t="inlineStr"/>
-      <c r="G25" s="8" t="inlineStr"/>
-      <c r="H25" s="8" t="inlineStr"/>
-      <c r="I25" s="8" t="inlineStr"/>
+      <c r="A25" s="8" t="inlineStr"/>
+      <c r="B25" s="8" t="inlineStr"/>
+      <c r="C25" s="8" t="inlineStr"/>
+      <c r="D25" s="9" t="inlineStr"/>
+      <c r="E25" s="9" t="inlineStr"/>
+      <c r="F25" s="10" t="inlineStr"/>
+      <c r="G25" s="10" t="inlineStr"/>
+      <c r="H25" s="10" t="inlineStr"/>
+      <c r="I25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr"/>
-      <c r="B26" s="6" t="inlineStr"/>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="7" t="inlineStr"/>
-      <c r="E26" s="7" t="inlineStr"/>
-      <c r="F26" s="8" t="inlineStr"/>
-      <c r="G26" s="8" t="inlineStr"/>
-      <c r="H26" s="8" t="inlineStr"/>
-      <c r="I26" s="8" t="inlineStr"/>
+      <c r="A26" s="8" t="inlineStr"/>
+      <c r="B26" s="8" t="inlineStr"/>
+      <c r="C26" s="8" t="inlineStr"/>
+      <c r="D26" s="9" t="inlineStr"/>
+      <c r="E26" s="9" t="inlineStr"/>
+      <c r="F26" s="10" t="inlineStr"/>
+      <c r="G26" s="10" t="inlineStr"/>
+      <c r="H26" s="10" t="inlineStr"/>
+      <c r="I26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr"/>
-      <c r="B27" s="6" t="inlineStr"/>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="7" t="inlineStr"/>
-      <c r="E27" s="7" t="inlineStr"/>
-      <c r="F27" s="8" t="inlineStr"/>
-      <c r="G27" s="8" t="inlineStr"/>
-      <c r="H27" s="8" t="inlineStr"/>
-      <c r="I27" s="8" t="inlineStr"/>
+      <c r="A27" s="8" t="inlineStr"/>
+      <c r="B27" s="8" t="inlineStr"/>
+      <c r="C27" s="8" t="inlineStr"/>
+      <c r="D27" s="9" t="inlineStr"/>
+      <c r="E27" s="9" t="inlineStr"/>
+      <c r="F27" s="10" t="inlineStr"/>
+      <c r="G27" s="10" t="inlineStr"/>
+      <c r="H27" s="10" t="inlineStr"/>
+      <c r="I27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr"/>
-      <c r="B28" s="6" t="inlineStr"/>
-      <c r="C28" s="6" t="inlineStr"/>
-      <c r="D28" s="7" t="inlineStr"/>
-      <c r="E28" s="7" t="inlineStr"/>
-      <c r="F28" s="8" t="inlineStr"/>
-      <c r="G28" s="8" t="inlineStr"/>
-      <c r="H28" s="8" t="inlineStr"/>
-      <c r="I28" s="8" t="inlineStr"/>
+      <c r="A28" s="8" t="inlineStr"/>
+      <c r="B28" s="8" t="inlineStr"/>
+      <c r="C28" s="8" t="inlineStr"/>
+      <c r="D28" s="9" t="inlineStr"/>
+      <c r="E28" s="9" t="inlineStr"/>
+      <c r="F28" s="10" t="inlineStr"/>
+      <c r="G28" s="10" t="inlineStr"/>
+      <c r="H28" s="10" t="inlineStr"/>
+      <c r="I28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr"/>
-      <c r="B29" s="6" t="inlineStr"/>
-      <c r="C29" s="6" t="inlineStr"/>
-      <c r="D29" s="7" t="inlineStr"/>
-      <c r="E29" s="7" t="inlineStr"/>
-      <c r="F29" s="8" t="inlineStr"/>
-      <c r="G29" s="8" t="inlineStr"/>
-      <c r="H29" s="8" t="inlineStr"/>
-      <c r="I29" s="8" t="inlineStr"/>
+      <c r="A29" s="8" t="inlineStr"/>
+      <c r="B29" s="8" t="inlineStr"/>
+      <c r="C29" s="8" t="inlineStr"/>
+      <c r="D29" s="9" t="inlineStr"/>
+      <c r="E29" s="9" t="inlineStr"/>
+      <c r="F29" s="10" t="inlineStr"/>
+      <c r="G29" s="10" t="inlineStr"/>
+      <c r="H29" s="10" t="inlineStr"/>
+      <c r="I29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr"/>
-      <c r="B30" s="6" t="inlineStr"/>
-      <c r="C30" s="6" t="inlineStr"/>
-      <c r="D30" s="7" t="inlineStr"/>
-      <c r="E30" s="7" t="inlineStr"/>
-      <c r="F30" s="8" t="inlineStr"/>
-      <c r="G30" s="8" t="inlineStr"/>
-      <c r="H30" s="8" t="inlineStr"/>
-      <c r="I30" s="8" t="inlineStr"/>
+      <c r="A30" s="8" t="inlineStr"/>
+      <c r="B30" s="8" t="inlineStr"/>
+      <c r="C30" s="8" t="inlineStr"/>
+      <c r="D30" s="9" t="inlineStr"/>
+      <c r="E30" s="9" t="inlineStr"/>
+      <c r="F30" s="10" t="inlineStr"/>
+      <c r="G30" s="10" t="inlineStr"/>
+      <c r="H30" s="10" t="inlineStr"/>
+      <c r="I30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr"/>
-      <c r="B31" s="6" t="inlineStr"/>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="7" t="inlineStr"/>
-      <c r="E31" s="7" t="inlineStr"/>
-      <c r="F31" s="8" t="inlineStr"/>
-      <c r="G31" s="8" t="inlineStr"/>
-      <c r="H31" s="8" t="inlineStr"/>
-      <c r="I31" s="8" t="inlineStr"/>
+      <c r="A31" s="8" t="inlineStr"/>
+      <c r="B31" s="8" t="inlineStr"/>
+      <c r="C31" s="8" t="inlineStr"/>
+      <c r="D31" s="9" t="inlineStr"/>
+      <c r="E31" s="9" t="inlineStr"/>
+      <c r="F31" s="10" t="inlineStr"/>
+      <c r="G31" s="10" t="inlineStr"/>
+      <c r="H31" s="10" t="inlineStr"/>
+      <c r="I31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr"/>
-      <c r="B32" s="6" t="inlineStr"/>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="7" t="inlineStr"/>
-      <c r="E32" s="7" t="inlineStr"/>
-      <c r="F32" s="8" t="inlineStr"/>
-      <c r="G32" s="8" t="inlineStr"/>
-      <c r="H32" s="8" t="inlineStr"/>
-      <c r="I32" s="8" t="inlineStr"/>
+      <c r="A32" s="8" t="inlineStr"/>
+      <c r="B32" s="8" t="inlineStr"/>
+      <c r="C32" s="8" t="inlineStr"/>
+      <c r="D32" s="9" t="inlineStr"/>
+      <c r="E32" s="9" t="inlineStr"/>
+      <c r="F32" s="10" t="inlineStr"/>
+      <c r="G32" s="10" t="inlineStr"/>
+      <c r="H32" s="10" t="inlineStr"/>
+      <c r="I32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr"/>
-      <c r="B33" s="6" t="inlineStr"/>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="7" t="inlineStr"/>
-      <c r="E33" s="7" t="inlineStr"/>
-      <c r="F33" s="8" t="inlineStr"/>
-      <c r="G33" s="8" t="inlineStr"/>
-      <c r="H33" s="8" t="inlineStr"/>
-      <c r="I33" s="8" t="inlineStr"/>
+      <c r="A33" s="8" t="inlineStr"/>
+      <c r="B33" s="8" t="inlineStr"/>
+      <c r="C33" s="8" t="inlineStr"/>
+      <c r="D33" s="9" t="inlineStr"/>
+      <c r="E33" s="9" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr"/>
+      <c r="G33" s="10" t="inlineStr"/>
+      <c r="H33" s="10" t="inlineStr"/>
+      <c r="I33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr"/>
-      <c r="B34" s="6" t="inlineStr"/>
-      <c r="C34" s="6" t="inlineStr"/>
-      <c r="D34" s="7" t="inlineStr"/>
-      <c r="E34" s="7" t="inlineStr"/>
-      <c r="F34" s="8" t="inlineStr"/>
-      <c r="G34" s="8" t="inlineStr"/>
-      <c r="H34" s="8" t="inlineStr"/>
-      <c r="I34" s="8" t="inlineStr"/>
+      <c r="A34" s="8" t="inlineStr"/>
+      <c r="B34" s="8" t="inlineStr"/>
+      <c r="C34" s="8" t="inlineStr"/>
+      <c r="D34" s="9" t="inlineStr"/>
+      <c r="E34" s="9" t="inlineStr"/>
+      <c r="F34" s="10" t="inlineStr"/>
+      <c r="G34" s="10" t="inlineStr"/>
+      <c r="H34" s="10" t="inlineStr"/>
+      <c r="I34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr"/>
-      <c r="B35" s="6" t="inlineStr"/>
-      <c r="C35" s="6" t="inlineStr"/>
-      <c r="D35" s="7" t="inlineStr"/>
-      <c r="E35" s="7" t="inlineStr"/>
-      <c r="F35" s="8" t="inlineStr"/>
-      <c r="G35" s="8" t="inlineStr"/>
-      <c r="H35" s="8" t="inlineStr"/>
-      <c r="I35" s="8" t="inlineStr"/>
+      <c r="A35" s="8" t="inlineStr"/>
+      <c r="B35" s="8" t="inlineStr"/>
+      <c r="C35" s="8" t="inlineStr"/>
+      <c r="D35" s="9" t="inlineStr"/>
+      <c r="E35" s="9" t="inlineStr"/>
+      <c r="F35" s="10" t="inlineStr"/>
+      <c r="G35" s="10" t="inlineStr"/>
+      <c r="H35" s="10" t="inlineStr"/>
+      <c r="I35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr"/>
-      <c r="B36" s="6" t="inlineStr"/>
-      <c r="C36" s="6" t="inlineStr"/>
-      <c r="D36" s="7" t="inlineStr"/>
-      <c r="E36" s="7" t="inlineStr"/>
-      <c r="F36" s="8" t="inlineStr"/>
-      <c r="G36" s="8" t="inlineStr"/>
-      <c r="H36" s="8" t="inlineStr"/>
-      <c r="I36" s="8" t="inlineStr"/>
+      <c r="A36" s="8" t="inlineStr"/>
+      <c r="B36" s="8" t="inlineStr"/>
+      <c r="C36" s="8" t="inlineStr"/>
+      <c r="D36" s="9" t="inlineStr"/>
+      <c r="E36" s="9" t="inlineStr"/>
+      <c r="F36" s="10" t="inlineStr"/>
+      <c r="G36" s="10" t="inlineStr"/>
+      <c r="H36" s="10" t="inlineStr"/>
+      <c r="I36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr"/>
-      <c r="B37" s="6" t="inlineStr"/>
-      <c r="C37" s="6" t="inlineStr"/>
-      <c r="D37" s="7" t="inlineStr"/>
-      <c r="E37" s="7" t="inlineStr"/>
-      <c r="F37" s="8" t="inlineStr"/>
-      <c r="G37" s="8" t="inlineStr"/>
-      <c r="H37" s="8" t="inlineStr"/>
-      <c r="I37" s="8" t="inlineStr"/>
+      <c r="A37" s="8" t="inlineStr"/>
+      <c r="B37" s="8" t="inlineStr"/>
+      <c r="C37" s="8" t="inlineStr"/>
+      <c r="D37" s="9" t="inlineStr"/>
+      <c r="E37" s="9" t="inlineStr"/>
+      <c r="F37" s="10" t="inlineStr"/>
+      <c r="G37" s="10" t="inlineStr"/>
+      <c r="H37" s="10" t="inlineStr"/>
+      <c r="I37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr"/>
-      <c r="B38" s="6" t="inlineStr"/>
-      <c r="C38" s="6" t="inlineStr"/>
-      <c r="D38" s="7" t="inlineStr"/>
-      <c r="E38" s="7" t="inlineStr"/>
-      <c r="F38" s="8" t="inlineStr"/>
-      <c r="G38" s="8" t="inlineStr"/>
-      <c r="H38" s="8" t="inlineStr"/>
-      <c r="I38" s="8" t="inlineStr"/>
+      <c r="A38" s="8" t="inlineStr"/>
+      <c r="B38" s="8" t="inlineStr"/>
+      <c r="C38" s="8" t="inlineStr"/>
+      <c r="D38" s="9" t="inlineStr"/>
+      <c r="E38" s="9" t="inlineStr"/>
+      <c r="F38" s="10" t="inlineStr"/>
+      <c r="G38" s="10" t="inlineStr"/>
+      <c r="H38" s="10" t="inlineStr"/>
+      <c r="I38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr"/>
-      <c r="B39" s="6" t="inlineStr"/>
-      <c r="C39" s="6" t="inlineStr"/>
-      <c r="D39" s="7" t="inlineStr"/>
-      <c r="E39" s="7" t="inlineStr"/>
-      <c r="F39" s="8" t="inlineStr"/>
-      <c r="G39" s="8" t="inlineStr"/>
-      <c r="H39" s="8" t="inlineStr"/>
-      <c r="I39" s="8" t="inlineStr"/>
+      <c r="A39" s="8" t="inlineStr"/>
+      <c r="B39" s="8" t="inlineStr"/>
+      <c r="C39" s="8" t="inlineStr"/>
+      <c r="D39" s="9" t="inlineStr"/>
+      <c r="E39" s="9" t="inlineStr"/>
+      <c r="F39" s="10" t="inlineStr"/>
+      <c r="G39" s="10" t="inlineStr"/>
+      <c r="H39" s="10" t="inlineStr"/>
+      <c r="I39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr"/>
-      <c r="B40" s="6" t="inlineStr"/>
-      <c r="C40" s="6" t="inlineStr"/>
-      <c r="D40" s="7" t="inlineStr"/>
-      <c r="E40" s="7" t="inlineStr"/>
-      <c r="F40" s="8" t="inlineStr"/>
-      <c r="G40" s="8" t="inlineStr"/>
-      <c r="H40" s="8" t="inlineStr"/>
-      <c r="I40" s="8" t="inlineStr"/>
+      <c r="A40" s="8" t="inlineStr"/>
+      <c r="B40" s="8" t="inlineStr"/>
+      <c r="C40" s="8" t="inlineStr"/>
+      <c r="D40" s="9" t="inlineStr"/>
+      <c r="E40" s="9" t="inlineStr"/>
+      <c r="F40" s="10" t="inlineStr"/>
+      <c r="G40" s="10" t="inlineStr"/>
+      <c r="H40" s="10" t="inlineStr"/>
+      <c r="I40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr"/>
-      <c r="B41" s="6" t="inlineStr"/>
-      <c r="C41" s="6" t="inlineStr"/>
-      <c r="D41" s="7" t="inlineStr"/>
-      <c r="E41" s="7" t="inlineStr"/>
-      <c r="F41" s="8" t="inlineStr"/>
-      <c r="G41" s="8" t="inlineStr"/>
-      <c r="H41" s="8" t="inlineStr"/>
-      <c r="I41" s="8" t="inlineStr"/>
+      <c r="A41" s="8" t="inlineStr"/>
+      <c r="B41" s="8" t="inlineStr"/>
+      <c r="C41" s="8" t="inlineStr"/>
+      <c r="D41" s="9" t="inlineStr"/>
+      <c r="E41" s="9" t="inlineStr"/>
+      <c r="F41" s="10" t="inlineStr"/>
+      <c r="G41" s="10" t="inlineStr"/>
+      <c r="H41" s="10" t="inlineStr"/>
+      <c r="I41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr"/>
-      <c r="B42" s="6" t="inlineStr"/>
-      <c r="C42" s="6" t="inlineStr"/>
-      <c r="D42" s="7" t="inlineStr"/>
-      <c r="E42" s="7" t="inlineStr"/>
-      <c r="F42" s="8" t="inlineStr"/>
-      <c r="G42" s="8" t="inlineStr"/>
-      <c r="H42" s="8" t="inlineStr"/>
-      <c r="I42" s="8" t="inlineStr"/>
+      <c r="A42" s="8" t="inlineStr"/>
+      <c r="B42" s="8" t="inlineStr"/>
+      <c r="C42" s="8" t="inlineStr"/>
+      <c r="D42" s="9" t="inlineStr"/>
+      <c r="E42" s="9" t="inlineStr"/>
+      <c r="F42" s="10" t="inlineStr"/>
+      <c r="G42" s="10" t="inlineStr"/>
+      <c r="H42" s="10" t="inlineStr"/>
+      <c r="I42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr"/>
-      <c r="B43" s="6" t="inlineStr"/>
-      <c r="C43" s="6" t="inlineStr"/>
-      <c r="D43" s="7" t="inlineStr"/>
-      <c r="E43" s="7" t="inlineStr"/>
-      <c r="F43" s="8" t="inlineStr"/>
-      <c r="G43" s="8" t="inlineStr"/>
-      <c r="H43" s="8" t="inlineStr"/>
-      <c r="I43" s="8" t="inlineStr"/>
+      <c r="A43" s="8" t="inlineStr"/>
+      <c r="B43" s="8" t="inlineStr"/>
+      <c r="C43" s="8" t="inlineStr"/>
+      <c r="D43" s="9" t="inlineStr"/>
+      <c r="E43" s="9" t="inlineStr"/>
+      <c r="F43" s="10" t="inlineStr"/>
+      <c r="G43" s="10" t="inlineStr"/>
+      <c r="H43" s="10" t="inlineStr"/>
+      <c r="I43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr"/>
-      <c r="B44" s="6" t="inlineStr"/>
-      <c r="C44" s="6" t="inlineStr"/>
-      <c r="D44" s="7" t="inlineStr"/>
-      <c r="E44" s="7" t="inlineStr"/>
-      <c r="F44" s="8" t="inlineStr"/>
-      <c r="G44" s="8" t="inlineStr"/>
-      <c r="H44" s="8" t="inlineStr"/>
-      <c r="I44" s="8" t="inlineStr"/>
+      <c r="A44" s="8" t="inlineStr"/>
+      <c r="B44" s="8" t="inlineStr"/>
+      <c r="C44" s="8" t="inlineStr"/>
+      <c r="D44" s="9" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr"/>
+      <c r="F44" s="10" t="inlineStr"/>
+      <c r="G44" s="10" t="inlineStr"/>
+      <c r="H44" s="10" t="inlineStr"/>
+      <c r="I44" s="10" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr"/>
+      <c r="B45" s="8" t="inlineStr"/>
+      <c r="C45" s="8" t="inlineStr"/>
+      <c r="D45" s="9" t="inlineStr"/>
+      <c r="E45" s="9" t="inlineStr"/>
+      <c r="F45" s="10" t="inlineStr"/>
+      <c r="G45" s="10" t="inlineStr"/>
+      <c r="H45" s="10" t="inlineStr"/>
+      <c r="I45" s="10" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr"/>
+      <c r="B46" s="8" t="inlineStr"/>
+      <c r="C46" s="8" t="inlineStr"/>
+      <c r="D46" s="9" t="inlineStr"/>
+      <c r="E46" s="9" t="inlineStr"/>
+      <c r="F46" s="10" t="inlineStr"/>
+      <c r="G46" s="10" t="inlineStr"/>
+      <c r="H46" s="10" t="inlineStr"/>
+      <c r="I46" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
